--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.64591731907019</v>
+        <v>10.66746156434891</v>
       </c>
       <c r="D2" t="n">
-        <v>64.98754815471062</v>
+        <v>10.56047657514048</v>
       </c>
       <c r="E2" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F2" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.32256034681976</v>
+        <v>10.93991605635821</v>
       </c>
       <c r="D3" t="n">
-        <v>66.29115920117133</v>
+        <v>10.77231337019034</v>
       </c>
       <c r="E3" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F3" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.53458438044806</v>
+        <v>10.32436996182281</v>
       </c>
       <c r="D4" t="n">
-        <v>62.66549911744941</v>
+        <v>10.18314360658553</v>
       </c>
       <c r="E4" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F4" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.64134858276842</v>
+        <v>8.716719144699869</v>
       </c>
       <c r="D5" t="n">
-        <v>53.46980896328253</v>
+        <v>8.688843956533411</v>
       </c>
       <c r="E5" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F5" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.88484056100224</v>
+        <v>7.131286591162865</v>
       </c>
       <c r="D6" t="n">
-        <v>42.59352880432252</v>
+        <v>6.92144843070241</v>
       </c>
       <c r="E6" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F6" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.77332333834887</v>
+        <v>7.763165042481691</v>
       </c>
       <c r="D7" t="n">
-        <v>46.56741457570168</v>
+        <v>7.567204868551523</v>
       </c>
       <c r="E7" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F7" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.53819329655217</v>
+        <v>6.749956410689729</v>
       </c>
       <c r="D8" t="n">
-        <v>30.67572330035593</v>
+        <v>4.984805036307839</v>
       </c>
       <c r="E8" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F8" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.98098001240746</v>
+        <v>3.571909252016213</v>
       </c>
       <c r="D9" t="n">
-        <v>22.68362450712636</v>
+        <v>3.686088982408033</v>
       </c>
       <c r="E9" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F9" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.42254005529836</v>
+        <v>4.943662758985983</v>
       </c>
       <c r="D10" t="n">
-        <v>31.31175772084284</v>
+        <v>5.088160629636961</v>
       </c>
       <c r="E10" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F10" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.74755038612921</v>
+        <v>7.921476937745997</v>
       </c>
       <c r="D11" t="n">
-        <v>16.62077013859466</v>
+        <v>2.700875147521633</v>
       </c>
       <c r="E11" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F11" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.11408623903409</v>
+        <v>5.381039013843041</v>
       </c>
       <c r="D12" t="n">
-        <v>32.54066821326494</v>
+        <v>5.287858584655553</v>
       </c>
       <c r="E12" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F12" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.84052127012594</v>
+        <v>5.011584706395466</v>
       </c>
       <c r="D13" t="n">
-        <v>31.16942790778332</v>
+        <v>5.06503203501479</v>
       </c>
       <c r="E13" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F13" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>11.49726852821854</v>
+        <v>1.868306135835513</v>
       </c>
       <c r="D14" t="n">
-        <v>11.42820485556006</v>
+        <v>1.857083289028509</v>
       </c>
       <c r="E14" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F14" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6.951915474036849</v>
+        <v>1.129686264530988</v>
       </c>
       <c r="D15" t="n">
-        <v>7.272036831611048</v>
+        <v>1.181705985136795</v>
       </c>
       <c r="E15" t="n">
-        <v>18.41488240137312</v>
+        <v>2.992418390223133</v>
       </c>
       <c r="F15" t="n">
-        <v>18.85636271653548</v>
+        <v>3.064158941437015</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
